--- a/SuppXLS/Scen_Peak_RSV-FLX.xlsx
+++ b/SuppXLS/Scen_Peak_RSV-FLX.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduumb-my.sharepoint.com/personal/meselu_tegenie_mellaku_nmbu_no/Documents/Documents/GitHub/MANU2025/SuppXLS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{BCAA6505-7DC0-4077-921D-E0165E2323A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93BB6CFE-A933-424A-8731-BBF0CC3079D0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB6DE19-ABD0-4A38-A58F-1AC1DDC76971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4215" yWindow="2535" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Peak_RSV-FLX" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcOnSave="0" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>Pset_CI</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t>DayNite</t>
+  </si>
+  <si>
+    <t>COM_PKFLX is not necessary since the time sclice in the modeling is 24 hrs</t>
   </si>
 </sst>
 </file>
@@ -286,7 +289,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 10" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normale_Scen_UC_IND-StrucConst" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -702,30 +705,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="5" max="5" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" customWidth="1"/>
+    <col min="10" max="11" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="8.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
@@ -738,7 +741,7 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
@@ -788,7 +791,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -812,7 +815,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>21</v>
       </c>
@@ -836,7 +839,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="11" t="s">
         <v>23</v>
@@ -846,7 +849,7 @@
         <v>17</v>
       </c>
       <c r="E6">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="I6" s="9">
         <v>0.1</v>
@@ -861,7 +864,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="11" t="s">
         <v>23</v>
@@ -886,7 +889,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -899,6 +902,11 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
     </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
